--- a/data/mcp_ecosystem_token_usage_correlation.xlsx
+++ b/data/mcp_ecosystem_token_usage_correlation.xlsx
@@ -16,6 +16,9 @@
     <sheet name="GitHub Stars" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="MCP Server Count" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Sources &amp; Methodology" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="LLM Revenue Run-Rate" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="LLM GitHub Commits" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Token Usage by Provider" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,10 +27,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -44,6 +48,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002E75B6"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="14"/>
     </font>
@@ -57,11 +66,6 @@
     </font>
     <font>
       <color rgb="009C0006"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="002E75B6"/>
-      <sz val="12"/>
     </font>
     <font>
       <sz val="10"/>
@@ -135,24 +139,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -594,6 +598,905 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>LLM Provider Revenue Run-Rate ($M ARR)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$B$2:$B$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$C$2:$C$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A5A5A5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$D$2:$D$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$E$2:$E$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B9BD5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$F$2:$F$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$G$2:$G$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="264478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$H$2:$H$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9B59B6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$I$2:$I$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="8"/>
+          <order val="8"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!J1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2ECC71"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$J$2:$J$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="9"/>
+          <order val="9"/>
+          <tx>
+            <strRef>
+              <f>'LLM Revenue Run-Rate'!K1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E74C3C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM Revenue Run-Rate'!$K$2:$K$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>ARR ($M)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>LLM Provider GitHub Commits (Quarterly)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$B$2:$B$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$C$2:$C$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A5A5A5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$D$2:$D$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$E$2:$E$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B9BD5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$F$2:$F$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$G$2:$G$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="264478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$H$2:$H$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="7"/>
+          <order val="7"/>
+          <tx>
+            <strRef>
+              <f>'LLM GitHub Commits'!I1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="9B59B6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'LLM GitHub Commits'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LLM GitHub Commits'!$I$2:$I$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Commits</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Daily Token Volume by Provider (Trillions)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4472C4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$B$2:$B$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!C1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="ED7D31"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$C$2:$C$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!D1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="A5A5A5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$D$2:$D$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="FFC000"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$E$2:$E$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!F1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="5B9BD5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$F$2:$F$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!G1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="70AD47"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$G$2:$G$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="6"/>
+          <order val="6"/>
+          <tx>
+            <strRef>
+              <f>'Token Usage by Provider'!H1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="264478"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Token Usage by Provider'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Token Usage by Provider'!$H$2:$H$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Tokens/Day (T)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0.0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -657,6 +1560,87 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="6480000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="6480000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="6480000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1724,6 +2708,2236 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Google Cloud
+(AI portion est.)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft
+Azure AI</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Meta / Llama
+(ad-AI rev est.)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mistral AI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>xAI / Grok</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>AWS Bedrock
+(AI portion est.)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Total LLM
+ARR ($M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q3</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>650</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>3070</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>6880</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>9650</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>12975</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>700</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>17445</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>25240</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>34875</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>16000</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>48657</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>12700</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>240</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>69940</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>300</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>105000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0066"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>OpenAI
+(openai-python
++tiktoken+whisper)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Anthropic
+(sdk-python
++claude-code)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Meta / Llama
+(llama+llama3
++llama-models)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Google
+(genai-python)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mistral AI
+(mistral-inference
++mistral-common)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DeepSeek
+(V3+R1)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>xAI / Grok
+(grok-1)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Cohere
+(cohere-python)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Total LLM
+Commits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q3</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>129</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>79</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>119</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>302</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>192</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>368</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="009933FF"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Google
+(Gemini + Search AI)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>OpenAI
+(ChatGPT + API)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Anthropic
+(Claude API)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Meta
+(Llama inference)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AWS
+(Bedrock + others)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>DeepSeek +
+Chinese OSS</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Other
+(Mistral, Cohere,
+xAI, Together, etc.)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Total Daily
+Tokens (T)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q3</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise API Market Share (% of spend)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>Mid-2025</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Meta / OSS</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Ventures</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Ventures</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A21:E21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4220,18 +7434,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4283,6 +7501,26 @@
           <t>npm Server Pkg Downloads</t>
         </is>
       </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Total LLM Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Total LLM GitHub Commits</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>OpenAI Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Anthropic Revenue ($M)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4314,6 +7552,18 @@
       <c r="I4" s="10" t="n">
         <v>0.887</v>
       </c>
+      <c r="J4" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="K4" s="11" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="M4" s="9" t="n">
+        <v>0.999</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -4345,6 +7595,18 @@
       <c r="I5" s="11" t="n">
         <v>-0.433</v>
       </c>
+      <c r="J5" s="11" t="n">
+        <v>-0.495</v>
+      </c>
+      <c r="K5" s="11" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L5" s="8" t="n">
+        <v>-0.517</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>-0.555</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -4376,6 +7638,18 @@
       <c r="I6" s="9" t="n">
         <v>0.964</v>
       </c>
+      <c r="J6" s="10" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="L6" s="10" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="M6" s="8" t="n">
+        <v>0.841</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4407,6 +7681,18 @@
       <c r="I7" s="9" t="n">
         <v>0.984</v>
       </c>
+      <c r="J7" s="10" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>0.85</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -4438,6 +7724,18 @@
       <c r="I8" s="10" t="n">
         <v>0.9370000000000001</v>
       </c>
+      <c r="J8" s="9" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0.995</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4469,6 +7767,18 @@
       <c r="I9" s="9" t="n">
         <v>0.967</v>
       </c>
+      <c r="J9" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="M9" s="10" t="n">
+        <v>0.925</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4500,6 +7810,18 @@
       <c r="I10" s="9" t="n">
         <v>0.985</v>
       </c>
+      <c r="J10" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>0.922</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4531,311 +7853,595 @@
       <c r="I11" s="7" t="n">
         <v>1</v>
       </c>
+      <c r="J11" s="9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>0.903</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Total LLM Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>-0.495</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0.979</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>0.981</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Total LLM GitHub Commits</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>-0.073</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="H13" s="11" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="I13" s="11" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="J13" s="11" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>-0.027</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>OpenAI Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>-0.517</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.9340000000000001</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>0.994</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="11" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Anthropic Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>-0.555</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>-0.027</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Key Findings</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>1. MCP SDK downloads correlate very strongly (r&gt;0.95) with industry-wide daily token volume and inference % of compute — MCP adoption is a proxy for the broader shift from training to inference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>2. MCP server count and GitHub stars show near-perfect correlation with inference compute share, suggesting MCP growth is tightly coupled with the inference-driven deployment wave.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>3. MCP GitHub commits show NEGATIVE correlation with downloads and token growth — development peaked in Q2 2025 while adoption continued accelerating. This is typical: tooling matures before ecosystem scale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>4. Hyperscaler capex correlates strongly with MCP downloads (r&gt;0.90) — infrastructure spending and MCP adoption are riding the same inference scaling wave.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>5. The training → inference shift (from 80/20 in 2022 to 25/75 in Q1 2026) is the macro driver: as inference dominates, tool integration standards like MCP become critical infrastructure.</t>
+          <t>1. MCP SDK downloads correlate very strongly (r&gt;0.95) with industry-wide daily token volume, inference % of compute, and total LLM revenue — MCP adoption scales with the entire inference economy.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr"/>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>2. OpenAI and Anthropic revenue each correlate r&gt;0.95 with MCP downloads — as these providers scale revenue (driven by token consumption), MCP tool integration grows in lockstep.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
-          <t>Interpretation: MCP is NOT driving token usage — it is being pulled forward BY the inference scaling wave. As more tokens are consumed in production (agentic, enterprise, consumer), the need for standardized tool integration grows proportionally.</t>
+          <t>3. MCP GitHub commits show NEGATIVE correlation with LLM revenue and token growth — MCP tooling matured in H1 2025 while the revenue and adoption curves continued steepening.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>4. Total LLM GitHub commits also show declining trends — model release repos (Llama, DeepSeek, Grok) have bursty patterns, while SDK repos (openai-python, anthropic-sdk) show steady maintenance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>5. Hyperscaler capex correlates strongly with both MCP downloads and LLM revenue (r&gt;0.90) — the same infrastructure investment wave is driving all three.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>6. The training→inference shift (20/80 in 2022 to 75/25 in Q1 2026) correlates with LLM revenue growth — revenue is an inference-side phenomenon (tokens consumed = revenue generated).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Interpretation: LLM provider revenue is essentially a derivative of inference token volume × price per token. MCP adoption is a derivative of inference deployment breadth. Both are pulled forward by the same macro force: the shift from training to inference as the dominant use of AI compute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Underlying Data (Active Quarters Only)</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>Quarter</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>MCP Total SDK Downloads</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>MCP GitHub Commits</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>MCP Server Count</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>MCP GitHub Stars</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>Daily Tokens (T)</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>Inference % of Compute</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>Hyperscaler Capex ($B)</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>npm Server Pkg Downloads</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>2024-Q4</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>116673</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>1910</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>81200</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2025-Q1</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>2401992</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>2308</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>42500</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H27" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>686000</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2025-Q2</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>41983661</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>3517</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>5867</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>82500</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="I28" s="3" t="n">
-        <v>2435200</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2025-Q3</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>77522633</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>2073</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>6550</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>118000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>118</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>5032500</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2025-Q4</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>270153893</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>1885</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>144700</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>140</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>5716500</v>
+      <c r="J30" s="1" t="inlineStr">
+        <is>
+          <t>Total LLM Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="K30" s="1" t="inlineStr">
+        <is>
+          <t>Total LLM GitHub Commits</t>
+        </is>
+      </c>
+      <c r="L30" s="1" t="inlineStr">
+        <is>
+          <t>OpenAI Revenue ($M)</t>
+        </is>
+      </c>
+      <c r="M30" s="1" t="inlineStr">
+        <is>
+          <t>Anthropic Revenue ($M)</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>116673</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1910</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>81200</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>17445</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>311</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>1800</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>2401992</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>2308</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>42500</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>686000</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>25240</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>369</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>41983661</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>3517</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>5867</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>82500</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>2435200</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>34875</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>77522633</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>2073</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6550</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>5032500</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>48657</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>270153893</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>1885</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>144700</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>5716500</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>69940</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>277</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>12700</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
           <t>2026-Q1</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n">
+      <c r="B36" s="3" t="n">
         <v>589191266</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C36" s="3" t="n">
         <v>1537</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>10500</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>169528</v>
       </c>
-      <c r="F31" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="G31" s="3" t="n">
+      <c r="G36" s="3" t="n">
         <v>0.75</v>
       </c>
-      <c r="H31" s="3" t="n">
+      <c r="H36" s="3" t="n">
         <v>165</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I36" s="3" t="n">
         <v>8151900</v>
       </c>
+      <c r="J36" s="3" t="n">
+        <v>105000</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>368</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>19000</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A17:I17"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A24:I24"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:I21"/>
-    <mergeCell ref="A16:I16"/>
+  <mergeCells count="11">
+    <mergeCell ref="A19:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A23:M23"/>
+    <mergeCell ref="A22:M22"/>
+    <mergeCell ref="A26:M26"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="A20:M20"/>
+    <mergeCell ref="A24:M24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5786,7 +9392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6039,6 +9645,222 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>LLM Revenue (OpenAI)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Reuters, The Information, OpenAI press</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>ARR milestones from published reports</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>2022 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>$3.5M (2020) → $25B ARR (Feb 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LLM Revenue (Anthropic)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>SaaStr, Reuters, Bloomberg</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>ARR milestones from funding/press reports</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>2023 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>$100M ARR (Sep 2023) → $19B ARR (Mar 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>LLM Revenue (Google Cloud AI)</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Alphabet SEC filings, earnings calls</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Google Cloud quarterly rev × est AI portion</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>2022 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>AI portion estimated at 5-20% of Cloud rev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>LLM Revenue (Azure AI)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Microsoft annual reports, earnings</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Azure AI run-rate from earnings commentary</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>2022 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>$4.7B RR (YE2024) → $13B RR (YE2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>LLM Revenue (Others)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>CB Insights, Crunchbase, press reports</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>ARR milestones from various sources</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>2023 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Mistral, Cohere, xAI, DeepSeek, AWS Bedrock</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>LLM GitHub Commits</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Stats API</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>commits list API with date range filters</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Q1 2022 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>14 repos across 8 providers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Token Usage by Provider</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Google/OpenAI earnings, a16z/OpenRouter</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Published provider volumes + mkt share estimates</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2022 – Q1 2026</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Estimates; Google disclosed 1.3Q/mo, OpenAI 8.6T/day</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise Mkt Share</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Menlo Ventures LLM reports</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Enterprise API spend surveys</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2023 – mid 2025</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Dollar-weighted market share</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mcp_ecosystem_token_usage_correlation.xlsx
+++ b/data/mcp_ecosystem_token_usage_correlation.xlsx
@@ -19,6 +19,7 @@
     <sheet name="LLM Revenue Run-Rate" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="LLM GitHub Commits" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Token Usage by Provider" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GitHub Platform Activity" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1497,6 +1498,108 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>GitHub Global Git Pushes (Quarterly)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GitHub Platform Activity'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="333333"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'GitHub Platform Activity'!$A$2:$A$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GitHub Platform Activity'!$B$2:$B$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Git Pushes</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="#,##0,,&quot;M&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1629,6 +1732,33 @@
       <col>0</col>
       <colOff>0</colOff>
       <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="11520000" cy="6480000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="11520000" cy="6480000"/>
@@ -4938,6 +5068,759 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00333333"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Quarter</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Git Pushes
+(Global)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Push QoQ
+Growth</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Push YoY
+Growth</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Active
+Developers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Dev QoQ
+Growth</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Total
+Repositories</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Pushes per
+Developer</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q1</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>140572256</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>0.09067307080704778</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.1590825157777029</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>89612163</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.07120588237895831</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>229733614</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>149717365</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.06505628678250708</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.1738912074275534</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>95043584</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.06061031023210539</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>243339989</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q3</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>146835949</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-0.01924570339586196</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.2642123768015416</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>100334892</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.05567243760504659</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>256393118</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2022-Q4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>161464841</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0.09962745567163522</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.252774615503373</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>105809362</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.05456197630630832</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>269935545</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q1</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>172765182</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.06998638793444822</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.2290133694660204</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>112142497</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.05985420269333064</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>283851980</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>175270480</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.01450117420071373</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.1706756928296194</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>118863203</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.05993005488365388</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>298254607</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q3</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>165466632</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-0.05593553460913669</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.1268809384001734</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>125462005</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.0555159362481592</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>311778148</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2023-Q4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>178868690</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0.08099553268238391</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.1077872364795505</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>131883095</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.05117955830532117</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>326068851</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>184167232</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.02962252365128859</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.06599738366264107</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>139575994</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.05833119855126245</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>340737253</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q2</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>189331668</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0.02804210034497334</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0.08022564895126671</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>145646544</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.04349279432679509</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>355510606</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q3</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>179232651</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-0.05334034769080465</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.08319513628584652</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>151993922</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.04358069766488937</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>369639247</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2024-Q4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>200262211</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0.1173310771372789</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0.1196046161013422</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>159142080</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0.04702923581378471</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>385466517</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>213071277</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.06396147299102783</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.1569445589538969</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>167884897</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.05493717940597476</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>402290482</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>247828515</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.1631249340097587</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0.3089649376563883</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>177219553</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.05560152322695244</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>420993825</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q3</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>250894326</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>0.01237069511553179</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.3998248901646833</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>189778233</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.07086509240884942</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>440152951</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph (official)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2025-Q4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>230201078</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-0.08247794332343727</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0.1494983344611132</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>198000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>0.04332302430068458</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>460000000</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Estimated from Octoverse 2025 (~1B commits, +25.1% YoY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-Q1</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>272731234</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0.1847522017251371</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>0.2799999973717715</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>0.06060606060606055</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>482000000</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Estimated (~28% YoY growth trajectory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Annual Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>Total Pushes</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>YoY Growth</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>Active Devs (YE)</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>598590411</v>
+      </c>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>105809362</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Innovation Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>692370984</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.1566690198784357</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>131883095</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Innovation Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>752993762</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.08755823019873987</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>159142080</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Innovation Graph</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>941995196</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>0.2509999996520555</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>198000000</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Octoverse 2025: ~1B commits, +25.1% YoY</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A21:E21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -9392,7 +10275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -9861,6 +10744,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GitHub Platform Activity</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>GitHub Innovation Graph + Octoverse</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>github/innovationgraph CSV data (git_pushes, developers, repos)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Q1 2020 – Q3 2025 official; Q4 2025, Q1 2026 estimated</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Git pushes ≈ commits proxy; Q4 2025 derived from Octoverse annual total</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
